--- a/tb.xlsx
+++ b/tb.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6edcc1c4ba920e4e/Desktop/project/GBSOV/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{97A92F1B-D6EC-439F-8734-F934DA47AF7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="35" documentId="8_{97A92F1B-D6EC-439F-8734-F934DA47AF7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{987818C7-F36E-4EE8-8FBB-A28BE0FEB3C2}"/>
   <bookViews>
-    <workbookView xWindow="4200" yWindow="2568" windowWidth="17280" windowHeight="8880" xr2:uid="{A3A1A61F-3E93-46BB-9329-84D77B09CE99}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{A3A1A61F-3E93-46BB-9329-84D77B09CE99}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -35,12 +35,116 @@
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="31">
+  <si>
+    <t>Company code</t>
+  </si>
+  <si>
+    <t>Profit center</t>
+  </si>
+  <si>
+    <t>Account number</t>
+  </si>
+  <si>
+    <t>Account description</t>
+  </si>
+  <si>
+    <t>Posting ISO</t>
+  </si>
+  <si>
+    <t>Functional area</t>
+  </si>
+  <si>
+    <t>Posting partner</t>
+  </si>
+  <si>
+    <t>Meridian</t>
+  </si>
+  <si>
+    <t>Posting local</t>
+  </si>
+  <si>
+    <t>Meridian  posting</t>
+  </si>
+  <si>
+    <t>Entity +GL+CC</t>
+  </si>
+  <si>
+    <t>J658</t>
+  </si>
+  <si>
+    <t>ADTL</t>
+  </si>
+  <si>
+    <t>Prof</t>
+  </si>
+  <si>
+    <t>EUR</t>
+  </si>
+  <si>
+    <t>EUDE</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>J659</t>
+  </si>
+  <si>
+    <t>J660</t>
+  </si>
+  <si>
+    <t>J661</t>
+  </si>
+  <si>
+    <t>J662</t>
+  </si>
+  <si>
+    <t>J663</t>
+  </si>
+  <si>
+    <t>J664</t>
+  </si>
+  <si>
+    <t>J665</t>
+  </si>
+  <si>
+    <t>J666</t>
+  </si>
+  <si>
+    <t>J667</t>
+  </si>
+  <si>
+    <t>J668</t>
+  </si>
+  <si>
+    <t>J669</t>
+  </si>
+  <si>
+    <t>J670</t>
+  </si>
+  <si>
+    <t>J671</t>
+  </si>
+  <si>
+    <t>J672</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -402,9 +506,537 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7165F11-2A36-4269-8E11-FD620BE8101B}">
-  <dimension ref="A1"/>
+  <dimension ref="A5:K20"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="12.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.21875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.21875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.21875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C5" t="s">
+        <v>2</v>
+      </c>
+      <c r="D5" t="s">
+        <v>3</v>
+      </c>
+      <c r="E5" t="s">
+        <v>4</v>
+      </c>
+      <c r="F5" t="s">
+        <v>5</v>
+      </c>
+      <c r="G5" t="s">
+        <v>6</v>
+      </c>
+      <c r="H5" t="s">
+        <v>7</v>
+      </c>
+      <c r="I5" t="s">
+        <v>8</v>
+      </c>
+      <c r="J5" t="s">
+        <v>9</v>
+      </c>
+      <c r="K5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6">
+        <v>6253400000</v>
+      </c>
+      <c r="D6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F6" t="s">
+        <v>15</v>
+      </c>
+      <c r="G6" t="s">
+        <v>16</v>
+      </c>
+      <c r="H6">
+        <v>64.75</v>
+      </c>
+      <c r="I6" t="s">
+        <v>14</v>
+      </c>
+      <c r="J6">
+        <v>51.75</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7">
+        <v>6253400001</v>
+      </c>
+      <c r="D7" t="s">
+        <v>13</v>
+      </c>
+      <c r="E7" t="s">
+        <v>14</v>
+      </c>
+      <c r="F7" t="s">
+        <v>15</v>
+      </c>
+      <c r="G7" t="s">
+        <v>16</v>
+      </c>
+      <c r="H7">
+        <v>65.75</v>
+      </c>
+      <c r="I7" t="s">
+        <v>14</v>
+      </c>
+      <c r="J7">
+        <v>58.74</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>18</v>
+      </c>
+      <c r="B8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C8">
+        <v>6253400002</v>
+      </c>
+      <c r="D8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E8" t="s">
+        <v>14</v>
+      </c>
+      <c r="F8" t="s">
+        <v>15</v>
+      </c>
+      <c r="G8" t="s">
+        <v>16</v>
+      </c>
+      <c r="H8">
+        <v>645.76</v>
+      </c>
+      <c r="I8" t="s">
+        <v>14</v>
+      </c>
+      <c r="J8">
+        <v>8550.51</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>19</v>
+      </c>
+      <c r="B9" t="s">
+        <v>12</v>
+      </c>
+      <c r="C9">
+        <v>6253400003</v>
+      </c>
+      <c r="D9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E9" t="s">
+        <v>14</v>
+      </c>
+      <c r="F9" t="s">
+        <v>15</v>
+      </c>
+      <c r="G9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H9">
+        <v>8657.23</v>
+      </c>
+      <c r="I9" t="s">
+        <v>14</v>
+      </c>
+      <c r="J9">
+        <v>54.75</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>20</v>
+      </c>
+      <c r="B10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C10">
+        <v>6253400004</v>
+      </c>
+      <c r="D10" t="s">
+        <v>13</v>
+      </c>
+      <c r="E10" t="s">
+        <v>14</v>
+      </c>
+      <c r="F10" t="s">
+        <v>15</v>
+      </c>
+      <c r="G10" t="s">
+        <v>16</v>
+      </c>
+      <c r="H10">
+        <v>754</v>
+      </c>
+      <c r="I10" t="s">
+        <v>14</v>
+      </c>
+      <c r="J10">
+        <v>55.75</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>21</v>
+      </c>
+      <c r="B11" t="s">
+        <v>12</v>
+      </c>
+      <c r="C11">
+        <v>6253400005</v>
+      </c>
+      <c r="D11" t="s">
+        <v>13</v>
+      </c>
+      <c r="E11" t="s">
+        <v>14</v>
+      </c>
+      <c r="F11" t="s">
+        <v>15</v>
+      </c>
+      <c r="G11" t="s">
+        <v>16</v>
+      </c>
+      <c r="H11">
+        <v>9875.3449999999993</v>
+      </c>
+      <c r="I11" t="s">
+        <v>14</v>
+      </c>
+      <c r="J11">
+        <v>64356.76</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>22</v>
+      </c>
+      <c r="B12" t="s">
+        <v>12</v>
+      </c>
+      <c r="C12">
+        <v>6253400006</v>
+      </c>
+      <c r="D12" t="s">
+        <v>13</v>
+      </c>
+      <c r="E12" t="s">
+        <v>14</v>
+      </c>
+      <c r="F12" t="s">
+        <v>15</v>
+      </c>
+      <c r="G12" t="s">
+        <v>16</v>
+      </c>
+      <c r="H12">
+        <v>75467.87</v>
+      </c>
+      <c r="I12" t="s">
+        <v>14</v>
+      </c>
+      <c r="J12">
+        <v>875.67</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>23</v>
+      </c>
+      <c r="B13" t="s">
+        <v>12</v>
+      </c>
+      <c r="C13">
+        <v>6253400007</v>
+      </c>
+      <c r="D13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E13" t="s">
+        <v>14</v>
+      </c>
+      <c r="F13" t="s">
+        <v>15</v>
+      </c>
+      <c r="G13" t="s">
+        <v>16</v>
+      </c>
+      <c r="H13">
+        <v>71.75</v>
+      </c>
+      <c r="I13" t="s">
+        <v>14</v>
+      </c>
+      <c r="J13">
+        <v>58.75</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>24</v>
+      </c>
+      <c r="B14" t="s">
+        <v>12</v>
+      </c>
+      <c r="C14">
+        <v>6253400008</v>
+      </c>
+      <c r="D14" t="s">
+        <v>13</v>
+      </c>
+      <c r="E14" t="s">
+        <v>14</v>
+      </c>
+      <c r="F14" t="s">
+        <v>15</v>
+      </c>
+      <c r="G14" t="s">
+        <v>16</v>
+      </c>
+      <c r="H14">
+        <v>72.75</v>
+      </c>
+      <c r="I14" t="s">
+        <v>14</v>
+      </c>
+      <c r="J14">
+        <v>59.75</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>25</v>
+      </c>
+      <c r="B15" t="s">
+        <v>12</v>
+      </c>
+      <c r="C15">
+        <v>6253400009</v>
+      </c>
+      <c r="D15" t="s">
+        <v>13</v>
+      </c>
+      <c r="E15" t="s">
+        <v>14</v>
+      </c>
+      <c r="F15" t="s">
+        <v>15</v>
+      </c>
+      <c r="G15" t="s">
+        <v>16</v>
+      </c>
+      <c r="H15">
+        <v>73.75</v>
+      </c>
+      <c r="I15" t="s">
+        <v>14</v>
+      </c>
+      <c r="J15">
+        <v>60.75</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>26</v>
+      </c>
+      <c r="B16" t="s">
+        <v>12</v>
+      </c>
+      <c r="C16">
+        <v>6253400010</v>
+      </c>
+      <c r="D16" t="s">
+        <v>13</v>
+      </c>
+      <c r="E16" t="s">
+        <v>14</v>
+      </c>
+      <c r="F16" t="s">
+        <v>15</v>
+      </c>
+      <c r="G16" t="s">
+        <v>16</v>
+      </c>
+      <c r="H16">
+        <v>74.75</v>
+      </c>
+      <c r="I16" t="s">
+        <v>14</v>
+      </c>
+      <c r="J16">
+        <v>61.75</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>27</v>
+      </c>
+      <c r="B17" t="s">
+        <v>12</v>
+      </c>
+      <c r="C17">
+        <v>6253400011</v>
+      </c>
+      <c r="D17" t="s">
+        <v>13</v>
+      </c>
+      <c r="E17" t="s">
+        <v>14</v>
+      </c>
+      <c r="F17" t="s">
+        <v>15</v>
+      </c>
+      <c r="G17" t="s">
+        <v>16</v>
+      </c>
+      <c r="H17">
+        <v>75.75</v>
+      </c>
+      <c r="I17" t="s">
+        <v>14</v>
+      </c>
+      <c r="J17">
+        <v>62.75</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>28</v>
+      </c>
+      <c r="B18" t="s">
+        <v>12</v>
+      </c>
+      <c r="C18">
+        <v>6253400012</v>
+      </c>
+      <c r="D18" t="s">
+        <v>13</v>
+      </c>
+      <c r="E18" t="s">
+        <v>14</v>
+      </c>
+      <c r="F18" t="s">
+        <v>15</v>
+      </c>
+      <c r="G18" t="s">
+        <v>16</v>
+      </c>
+      <c r="H18">
+        <v>76.75</v>
+      </c>
+      <c r="I18" t="s">
+        <v>14</v>
+      </c>
+      <c r="J18">
+        <v>63.75</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>29</v>
+      </c>
+      <c r="B19" t="s">
+        <v>12</v>
+      </c>
+      <c r="C19">
+        <v>6253400013</v>
+      </c>
+      <c r="D19" t="s">
+        <v>13</v>
+      </c>
+      <c r="E19" t="s">
+        <v>14</v>
+      </c>
+      <c r="F19" t="s">
+        <v>15</v>
+      </c>
+      <c r="G19" t="s">
+        <v>16</v>
+      </c>
+      <c r="H19">
+        <v>77.75</v>
+      </c>
+      <c r="I19" t="s">
+        <v>14</v>
+      </c>
+      <c r="J19">
+        <v>64.75</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>30</v>
+      </c>
+      <c r="B20" t="s">
+        <v>12</v>
+      </c>
+      <c r="C20">
+        <v>6253400014</v>
+      </c>
+      <c r="D20" t="s">
+        <v>13</v>
+      </c>
+      <c r="E20" t="s">
+        <v>14</v>
+      </c>
+      <c r="F20" t="s">
+        <v>15</v>
+      </c>
+      <c r="G20" t="s">
+        <v>16</v>
+      </c>
+      <c r="H20">
+        <v>78.75</v>
+      </c>
+      <c r="I20" t="s">
+        <v>14</v>
+      </c>
+      <c r="J20">
+        <v>65.75</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>